--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-en-rapport-avec-ald.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4707,7 +4707,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -5111,7 +5111,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>176</v>
       </c>
@@ -5126,13 +5126,13 @@
         <v>62</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5214,7 +5214,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>180</v>
       </c>
@@ -5229,13 +5229,13 @@
         <v>181</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5523,7 +5523,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>194</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
